--- a/PAINEL_MEDICAO.xlsx
+++ b/PAINEL_MEDICAO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe382923eb6bfb95/Área de Trabalho/EMPRESA/LEONE/ADMINISTRATIVO/ALEX/DASH_MENSAL/dashboard-financeiro-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe382923eb6bfb95/Área de Trabalho/EMPRESA/LEONE/ADMINISTRATIVO/ALEX/00 - DASH_MENSAL/dashboard-financeiro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{80296205-AFED-4F77-986A-C43D9A802F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC174C9E-6F20-446F-82B2-5F27795BC1B0}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="8_{80296205-AFED-4F77-986A-C43D9A802F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE58FCF6-6544-440F-A9BF-61A00184DFD3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D458C61B-3165-4ACA-B3D1-BE54D26DDE28}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="37">
   <si>
     <t>SAFRA</t>
   </si>
@@ -126,6 +126,30 @@
   </si>
   <si>
     <t>QUADRA CONFUSÃO</t>
+  </si>
+  <si>
+    <t>CONSTRUÇÃO 25 CASAS POPULARES</t>
+  </si>
+  <si>
+    <t>CAIXA ESCOLAR DELFINÓPOLIS</t>
+  </si>
+  <si>
+    <t>CONSTRUÇÃO 20 CASAS POPULARES</t>
+  </si>
+  <si>
+    <t>CEMEI ALVORADA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>UBS ITAGUARA</t>
+  </si>
+  <si>
+    <t>APLIAÇÃO UEMG CLÁUDIO</t>
+  </si>
+  <si>
+    <t>RESTAURANTE- IFMG IPATINGA</t>
+  </si>
+  <si>
+    <t>RESTAURANTE- IFMG ARCOS</t>
   </si>
 </sst>
 </file>
@@ -593,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78C61581-3CDE-422B-802B-087CF49FF933}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -731,11 +755,11 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46066</v>
+        <v>46101</v>
       </c>
       <c r="B7" s="1" t="str">
         <f>TEXT(A7,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-03</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>3</v>
@@ -747,16 +771,16 @@
         <v>19</v>
       </c>
       <c r="F7" s="5">
-        <v>4220.75</v>
+        <v>3361.9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46101</v>
+        <v>46066</v>
       </c>
       <c r="B8" s="1" t="str">
         <f>TEXT(A8,"AAAA-MM")</f>
-        <v>2026-03</v>
+        <v>2026-02</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
@@ -768,7 +792,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="5">
-        <v>84917.27</v>
+        <v>4220.75</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -789,7 +813,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="5">
-        <v>3361.9</v>
+        <v>84917.27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1004,14 +1028,14 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B20" s="1" t="str">
         <f>TEXT(A20,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>8</v>
@@ -1020,19 +1044,19 @@
         <v>19</v>
       </c>
       <c r="F20" s="5">
-        <v>53093.61</v>
+        <v>43069.62</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>TEXT(A21,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>8</v>
@@ -1041,7 +1065,7 @@
         <v>19</v>
       </c>
       <c r="F21" s="5">
-        <v>43069.62</v>
+        <v>53093.61</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1130,44 +1154,54 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>46184</v>
+        <v>46296</v>
       </c>
       <c r="B26" s="1" t="str">
         <f>TEXT(A26,"AAAA-MM")</f>
+        <v>2026-10</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="5">
+        <v>10713.61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <f>TEXT(A27,"AAAA-MM")</f>
         <v>2026-06</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="5">
+      <c r="D27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="5">
         <v>137681.63</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="5">
-        <v>33173.360000000001</v>
-      </c>
-    </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="1"/>
+      <c r="A28" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B28" s="1" t="str">
+        <f>TEXT(A28,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C28" s="4" t="s">
         <v>21</v>
       </c>
@@ -1178,7 +1212,7 @@
         <v>19</v>
       </c>
       <c r="F28" s="5">
-        <v>10713.61</v>
+        <v>33173.360000000001</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,7 +1233,7 @@
         <v>19</v>
       </c>
       <c r="F29" s="5">
-        <v>87470.6</v>
+        <v>10508.47</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1220,14 +1254,19 @@
         <v>19</v>
       </c>
       <c r="F30" s="5">
-        <v>10508.47</v>
+        <v>87470.6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="1"/>
+      <c r="A31" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B31" s="1" t="str">
+        <f>TEXT(A31,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C31" s="4" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>8</v>
@@ -1236,12 +1275,17 @@
         <v>19</v>
       </c>
       <c r="F31" s="5">
-        <v>5938.07</v>
+        <v>166317.79999999999</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" s="1"/>
+      <c r="A32" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B32" s="1" t="str">
+        <f>TEXT(A32,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C32" s="4" t="s">
         <v>3</v>
       </c>
@@ -1256,8 +1300,13 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="1"/>
+      <c r="A33" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B33" s="1" t="str">
+        <f>TEXT(A33,"AAAA-MM")</f>
+        <v>2026-08</v>
+      </c>
       <c r="C33" s="4" t="s">
         <v>3</v>
       </c>
@@ -1268,12 +1317,17 @@
         <v>19</v>
       </c>
       <c r="F33" s="5">
-        <v>109050.83</v>
+        <v>5938.07</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="1"/>
+      <c r="A34" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B34" s="1" t="str">
+        <f>TEXT(A34,"AAAA-MM")</f>
+        <v>2026-08</v>
+      </c>
       <c r="C34" s="4" t="s">
         <v>3</v>
       </c>
@@ -1288,8 +1342,13 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="1"/>
+      <c r="A35" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B35" s="1" t="str">
+        <f>TEXT(A35,"AAAA-MM")</f>
+        <v>2026-08</v>
+      </c>
       <c r="C35" s="4" t="s">
         <v>3</v>
       </c>
@@ -1304,10 +1363,15 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="1"/>
+      <c r="A36" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B36" s="1" t="str">
+        <f>TEXT(A36,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C36" s="4" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>8</v>
@@ -1316,12 +1380,17 @@
         <v>19</v>
       </c>
       <c r="F36" s="5">
-        <v>166317.79999999999</v>
+        <v>109050.83</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="1"/>
+      <c r="A37" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B37" s="1" t="str">
+        <f>TEXT(A37,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C37" s="4" t="s">
         <v>28</v>
       </c>
@@ -1332,12 +1401,17 @@
         <v>19</v>
       </c>
       <c r="F37" s="5">
-        <v>130602.76</v>
+        <v>4915.72</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="1"/>
+      <c r="A38" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B38" s="1" t="str">
+        <f>TEXT(A38,"AAAA-MM")</f>
+        <v>2026-08</v>
+      </c>
       <c r="C38" s="4" t="s">
         <v>28</v>
       </c>
@@ -1348,12 +1422,17 @@
         <v>19</v>
       </c>
       <c r="F38" s="5">
-        <v>4915.72</v>
+        <v>14780.71</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="1"/>
+      <c r="A39" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B39" s="1" t="str">
+        <f>TEXT(A39,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C39" s="4" t="s">
         <v>28</v>
       </c>
@@ -1364,394 +1443,384 @@
         <v>19</v>
       </c>
       <c r="F39" s="5">
-        <v>14780.71</v>
+        <v>130602.76</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>46031</v>
+        <v>46225</v>
       </c>
       <c r="B40" s="1" t="str">
         <f>TEXT(A40,"AAAA-MM")</f>
-        <v>2026-01</v>
+        <v>2026-07</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F40" s="5">
-        <v>175344.01</v>
+        <v>42091.28</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>46050</v>
+        <v>46238</v>
       </c>
       <c r="B41" s="1" t="str">
         <f>TEXT(A41,"AAAA-MM")</f>
-        <v>2026-01</v>
+        <v>2026-08</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F41" s="5">
-        <v>49479.11</v>
+        <v>41717.74</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>46055</v>
+        <v>46255</v>
       </c>
       <c r="B42" s="1" t="str">
         <f>TEXT(A42,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-08</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F42" s="5">
-        <v>82294.75</v>
+        <v>221876.19</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>46073</v>
+        <v>46244</v>
       </c>
       <c r="B43" s="1" t="str">
         <f>TEXT(A43,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-08</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F43" s="5">
-        <v>99660.65</v>
+        <v>192634.32</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>46066</v>
+        <v>46258</v>
       </c>
       <c r="B44" s="1" t="str">
         <f>TEXT(A44,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-08</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F44" s="5">
-        <v>33014.82</v>
+        <v>334667.15999999997</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>46086</v>
+        <v>46258</v>
       </c>
       <c r="B45" s="1" t="str">
         <f>TEXT(A45,"AAAA-MM")</f>
-        <v>2026-03</v>
+        <v>2026-08</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F45" s="5">
-        <v>113652.43</v>
+        <v>53709.72</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>46099</v>
+        <v>46260</v>
       </c>
       <c r="B46" s="1" t="str">
         <f>TEXT(A46,"AAAA-MM")</f>
-        <v>2026-03</v>
+        <v>2026-08</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F46" s="5">
-        <v>240884.01</v>
+        <v>113021.91</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>46100</v>
+        <v>46267</v>
       </c>
       <c r="B47" s="1" t="str">
         <f>TEXT(A47,"AAAA-MM")</f>
-        <v>2026-03</v>
+        <v>2026-09</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F47" s="5">
-        <v>118242.07</v>
+        <v>91095.12</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>46113</v>
+        <v>46296</v>
       </c>
       <c r="B48" s="1" t="str">
         <f>TEXT(A48,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <v>2026-10</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F48" s="5">
-        <v>9677.83</v>
+        <v>53153</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>46114</v>
+        <v>46296</v>
       </c>
       <c r="B49" s="1" t="str">
         <f>TEXT(A49,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <v>2026-10</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F49" s="5">
-        <v>49479.11</v>
+        <v>14232.5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>46119</v>
+        <v>46295</v>
       </c>
       <c r="B50" s="1" t="str">
         <f>TEXT(A50,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <v>2026-09</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F50" s="5">
-        <v>66130.100000000006</v>
+        <v>38569.46</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>46125</v>
+        <v>46294</v>
       </c>
       <c r="B51" s="1" t="str">
         <f>TEXT(A51,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <v>2026-09</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F51" s="5">
-        <v>16640.05</v>
+        <v>104516.52</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>46125</v>
+        <v>46321</v>
       </c>
       <c r="B52" s="1" t="str">
         <f>TEXT(A52,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <v>2026-10</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F52" s="5">
-        <v>17563.47</v>
+        <v>78871.89</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>46142</v>
+        <v>46289</v>
       </c>
       <c r="B53" s="1" t="str">
         <f>TEXT(A53,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <v>2026-09</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F53" s="5">
-        <v>53404.84</v>
+        <v>503269.9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>46140</v>
+        <v>46303</v>
       </c>
       <c r="B54" s="1" t="str">
         <f>TEXT(A54,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <v>2026-10</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F54" s="5">
-        <v>33014.82</v>
+        <v>8641.4500000000007</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>46154</v>
+        <v>46321</v>
       </c>
       <c r="B55" s="1" t="str">
         <f>TEXT(A55,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <v>2026-10</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F55" s="5">
-        <v>159944.82999999999</v>
+        <v>74041.3</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
-        <v>46169</v>
-      </c>
-      <c r="B56" s="1" t="str">
-        <f>TEXT(A56,"AAAA-MM")</f>
-        <v>2026-05</v>
-      </c>
+      <c r="A56" s="3"/>
+      <c r="B56" s="1"/>
       <c r="C56" s="4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F56" s="5">
-        <v>172055.23</v>
+        <v>109172.26</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
-        <v>46169</v>
-      </c>
-      <c r="B57" s="1" t="str">
-        <f>TEXT(A57,"AAAA-MM")</f>
-        <v>2026-05</v>
-      </c>
+      <c r="A57" s="3"/>
+      <c r="B57" s="1"/>
       <c r="C57" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F57" s="5">
-        <v>28101.02</v>
+        <v>122165.97</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>46154</v>
+        <v>46031</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f>TEXT(A58,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" ref="B58:B122" si="0">TEXT(A58,"AAAA-MM")</f>
+        <v>2026-01</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>22</v>
@@ -1763,19 +1832,19 @@
         <v>19</v>
       </c>
       <c r="F58" s="5">
-        <v>71475.05</v>
+        <v>175344.01</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>46154</v>
+        <v>46050</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f>TEXT(A59,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" si="0"/>
+        <v>2026-01</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>15</v>
@@ -1784,19 +1853,19 @@
         <v>19</v>
       </c>
       <c r="F59" s="5">
-        <v>62994.13</v>
+        <v>49479.11</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>46181</v>
+        <v>46055</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f>TEXT(A60,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-02</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>15</v>
@@ -1805,19 +1874,19 @@
         <v>19</v>
       </c>
       <c r="F60" s="5">
-        <v>12964.48</v>
+        <v>82294.75</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>46181</v>
+        <v>46073</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f>TEXT(A61,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-02</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>15</v>
@@ -1826,19 +1895,19 @@
         <v>19</v>
       </c>
       <c r="F61" s="5">
-        <v>43881.86</v>
+        <v>99660.65</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>46183</v>
+        <v>46066</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f>TEXT(A62,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-02</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>15</v>
@@ -1847,19 +1916,19 @@
         <v>19</v>
       </c>
       <c r="F62" s="5">
-        <v>116713.56</v>
+        <v>33014.82</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>46183</v>
+        <v>46086</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f>TEXT(A63,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-03</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>15</v>
@@ -1868,19 +1937,19 @@
         <v>19</v>
       </c>
       <c r="F63" s="5">
-        <v>12545.33</v>
+        <v>113652.43</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>46184</v>
+        <v>46099</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f>TEXT(A64,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-03</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>15</v>
@@ -1889,19 +1958,19 @@
         <v>19</v>
       </c>
       <c r="F64" s="5">
-        <v>49479.11</v>
+        <v>240884.01</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>46203</v>
+        <v>46100</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f>TEXT(A65,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-03</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>15</v>
@@ -1910,19 +1979,19 @@
         <v>19</v>
       </c>
       <c r="F65" s="5">
-        <v>23760.73</v>
+        <v>118242.07</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>46203</v>
+        <v>46113</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f>TEXT(A66,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-04</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>15</v>
@@ -1931,19 +2000,19 @@
         <v>19</v>
       </c>
       <c r="F66" s="5">
-        <v>14926.37</v>
+        <v>9677.83</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>46202</v>
+        <v>46114</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f>TEXT(A67,"AAAA-MM")</f>
-        <v>2026-06</v>
+        <f t="shared" si="0"/>
+        <v>2026-04</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>15</v>
@@ -1952,14 +2021,19 @@
         <v>19</v>
       </c>
       <c r="F67" s="5">
-        <v>79682.429999999993</v>
+        <v>49479.11</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-      <c r="B68" s="1"/>
+      <c r="A68" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B68" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-04</v>
+      </c>
       <c r="C68" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>15</v>
@@ -1968,14 +2042,19 @@
         <v>19</v>
       </c>
       <c r="F68" s="5">
-        <v>11922.88</v>
+        <v>66130.100000000006</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="1"/>
+      <c r="A69" s="3">
+        <v>46125</v>
+      </c>
+      <c r="B69" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-04</v>
+      </c>
       <c r="C69" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>15</v>
@@ -1984,12 +2063,17 @@
         <v>19</v>
       </c>
       <c r="F69" s="5">
-        <v>10036.26</v>
+        <v>16640.05</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="3"/>
-      <c r="B70" s="1"/>
+      <c r="A70" s="3">
+        <v>46125</v>
+      </c>
+      <c r="B70" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-04</v>
+      </c>
       <c r="C70" s="4" t="s">
         <v>14</v>
       </c>
@@ -2000,14 +2084,19 @@
         <v>19</v>
       </c>
       <c r="F70" s="5">
-        <v>89122.7</v>
+        <v>17563.47</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="1"/>
+      <c r="A71" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B71" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-04</v>
+      </c>
       <c r="C71" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>15</v>
@@ -2016,347 +2105,1731 @@
         <v>19</v>
       </c>
       <c r="F71" s="5">
-        <v>139858.12</v>
+        <v>53404.84</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46072</v>
+        <v>46140</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f>TEXT(A72,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <f t="shared" si="0"/>
+        <v>2026-04</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F72" s="5">
-        <v>283719.89</v>
+        <v>33014.82</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46052</v>
+        <v>46169</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f>TEXT(A73,"AAAA-MM")</f>
-        <v>2026-01</v>
+        <f t="shared" si="0"/>
+        <v>2026-05</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F73" s="5">
-        <v>37071.980000000003</v>
+        <v>28101.02</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46050</v>
+        <v>46154</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f>TEXT(A74,"AAAA-MM")</f>
-        <v>2026-01</v>
+        <f t="shared" si="0"/>
+        <v>2026-05</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F74" s="5">
-        <v>52435.14</v>
+        <v>159944.82999999999</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>46080</v>
+        <v>46169</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f>TEXT(A75,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <f t="shared" si="0"/>
+        <v>2026-05</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F75" s="5">
-        <v>21893.759999999998</v>
+        <v>172055.23</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46080</v>
+        <v>46154</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f>TEXT(A76,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <f t="shared" si="0"/>
+        <v>2026-05</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F76" s="5">
-        <v>33292.76</v>
+        <v>71475.05</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>46078</v>
+        <v>46154</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f>TEXT(A77,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <f t="shared" si="0"/>
+        <v>2026-05</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F77" s="5">
-        <v>1738.58</v>
+        <v>62994.13</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>46080</v>
+        <v>46181</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f>TEXT(A78,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <f t="shared" si="0"/>
+        <v>2026-06</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F78" s="5">
-        <v>4750.45</v>
+        <v>12964.48</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>46121</v>
+        <v>46181</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f>TEXT(A79,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <f t="shared" si="0"/>
+        <v>2026-06</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F79" s="5">
-        <v>62541.57</v>
+        <v>43881.86</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>46146</v>
+        <v>46183</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f>TEXT(A80,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" si="0"/>
+        <v>2026-06</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F80" s="5">
-        <v>55985.64</v>
+        <v>12545.33</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f>TEXT(A81,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" si="0"/>
+        <v>2026-06</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F81" s="5">
-        <v>154142.54</v>
+        <v>116713.56</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>46169</v>
+        <v>46184</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f>TEXT(A82,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" si="0"/>
+        <v>2026-06</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F82" s="5">
-        <v>51257.36</v>
+        <v>49479.11</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>46157</v>
+        <v>46203</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f>TEXT(A83,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" si="0"/>
+        <v>2026-06</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F83" s="5">
-        <v>320442.87</v>
+        <v>14926.37</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>46168</v>
+        <v>46203</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f>TEXT(A84,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" si="0"/>
+        <v>2026-06</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F84" s="5">
-        <v>20501.97</v>
+        <v>23760.73</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>46169</v>
+        <v>46216</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f>TEXT(A85,"AAAA-MM")</f>
-        <v>2026-05</v>
+        <f t="shared" si="0"/>
+        <v>2026-07</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F85" s="5">
-        <v>57227.58</v>
+        <v>11922.88</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>46184</v>
+        <v>46202</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f>TEXT(A86,"AAAA-MM")</f>
+        <f t="shared" si="0"/>
         <v>2026-06</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F86" s="5">
-        <v>45259.99</v>
+        <v>79682.429999999993</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B87" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="5">
+        <v>10036.26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>46217</v>
+      </c>
+      <c r="B88" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="5">
+        <v>89122.7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B89" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" s="5">
+        <v>139858.12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B90" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" s="5">
+        <v>93878.7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B91" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="5">
+        <v>15054.4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B92" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="5">
+        <v>94418.97</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B93" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" s="5">
+        <v>96478.14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B94" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="5">
+        <v>31694.95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B95" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="5">
+        <v>13465.64</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B96" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="5">
+        <v>3747.1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B97" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" s="5">
+        <v>96849.23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B98" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="5">
+        <v>22014.799999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B99" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" s="5">
+        <v>34934.97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B100" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" s="5">
+        <v>5430.18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B101" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" s="5">
+        <v>2420.13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>46324</v>
+      </c>
+      <c r="B102" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="5">
+        <v>65092.18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B103" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F103" s="5">
+        <v>17549.82</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B104" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" s="5">
+        <v>99246.86</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B105" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" s="5">
+        <v>17676.259999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B106" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" s="5">
+        <v>106449.52</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B107" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" s="5">
+        <v>86580.06</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>46294</v>
+      </c>
+      <c r="B108" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" s="5">
+        <v>29468.2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B109" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" s="5">
+        <v>40649.06</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>46324</v>
+      </c>
+      <c r="B110" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" s="5">
+        <v>60835.25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
+        <v>46301</v>
+      </c>
+      <c r="B111" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" s="5">
+        <v>92673.61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>46308</v>
+      </c>
+      <c r="B112" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="5">
+        <v>56984.76</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>46308</v>
+      </c>
+      <c r="B113" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" s="5">
+        <v>128556.8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>46324</v>
+      </c>
+      <c r="B114" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" s="5">
+        <v>107806.43</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" s="5">
+        <v>21038.45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116" s="5">
+        <v>3432.17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>46072</v>
+      </c>
+      <c r="B117" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-02</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F117" s="5">
+        <v>283719.89</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B118" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-01</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F118" s="5">
+        <v>37071.980000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>46050</v>
+      </c>
+      <c r="B119" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-01</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" s="5">
+        <v>52435.14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>46078</v>
+      </c>
+      <c r="B120" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-02</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120" s="5">
+        <v>1738.58</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B121" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-02</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" s="5">
+        <v>4750.45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B122" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>2026-02</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F122" s="5">
+        <v>21893.759999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B123" s="1" t="str">
+        <f t="shared" ref="B123:B151" si="1">TEXT(A123,"AAAA-MM")</f>
+        <v>2026-02</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" s="5">
+        <v>33292.76</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>46121</v>
+      </c>
+      <c r="B124" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-04</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F124" s="5">
+        <v>62541.57</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>46146</v>
+      </c>
+      <c r="B125" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-05</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F125" s="5">
+        <v>55985.64</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B126" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-05</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" s="5">
+        <v>154142.54</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B127" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-05</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F127" s="5">
+        <v>51257.36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B128" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-05</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F128" s="5">
+        <v>320442.87</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B129" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-05</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F129" s="5">
+        <v>20501.97</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B130" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-05</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130" s="5">
+        <v>57227.58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B131" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-06</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F131" s="5">
+        <v>45259.99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
         <v>46198</v>
       </c>
-      <c r="B87" s="1" t="str">
-        <f>TEXT(A87,"AAAA-MM")</f>
+      <c r="B132" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>2026-06</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C132" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D132" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="5">
+      <c r="E132" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F132" s="5">
         <v>44307.7</v>
       </c>
     </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B133" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F133" s="5">
+        <v>24677.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B134" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F134" s="5">
+        <v>149576.73000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B135" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F135" s="5">
+        <v>184349.64</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B136" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136" s="5">
+        <v>20189.830000000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B137" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F137" s="5">
+        <v>76425.11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B138" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" s="5">
+        <v>133855.48000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B139" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-07</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F139" s="5">
+        <v>273618.03999999998</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B140" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F140" s="5">
+        <v>27874.13</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B141" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F141" s="5">
+        <v>164077.28</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B142" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F142" s="5">
+        <v>3807.56</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B143" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F143" s="5">
+        <v>104039.54</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B144" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F144" s="5">
+        <v>32397.82</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B145" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-08</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F145" s="5">
+        <v>51675.26</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B146" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F146" s="5">
+        <v>44054.47</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B147" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F147" s="5">
+        <v>99448.46</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="3">
+        <v>46303</v>
+      </c>
+      <c r="B148" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-10</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F148" s="5">
+        <v>37130.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B149" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F149" s="5">
+        <v>3320.02</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B150" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>2026-09</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F150" s="5">
+        <v>3061.58</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="3"/>
+      <c r="B151" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>1900-01</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F151" s="5">
+        <v>18241.68</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="3"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F152" s="5">
+        <v>178045.05</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="3"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F153" s="5">
+        <v>96174.28</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="3"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F154" s="5">
+        <v>176034.85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F87" xr:uid="{78C61581-3CDE-422B-802B-087CF49FF933}"/>
+  <autoFilter ref="A1:F87" xr:uid="{78C61581-3CDE-422B-802B-087CF49FF933}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F87">
+      <sortCondition ref="A1:A87"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>